--- a/data/trans_bre/IP19C04-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 22,77</t>
+          <t>-7,4; 25,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 10,2</t>
+          <t>-19,3; 9,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 11,52</t>
+          <t>-10,19; 13,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 25,61</t>
+          <t>-5,37; 21,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 181,01</t>
+          <t>-99,4; 158,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,14 +695,14 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 3,7</t>
+          <t>-9,01; 4,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 11,43</t>
+          <t>-0,96; 11,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 0,97</t>
+          <t>-12,57; 0,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 6,33</t>
+          <t>-2,9; 6,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-87,11; 122,19</t>
+          <t>-87,4; 203,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,64; —</t>
+          <t>-59,2; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 168,17</t>
+          <t>-100,0; 74,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 19,47</t>
+          <t>0,29; 17,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 16,94</t>
+          <t>0,0; 19,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 0,0</t>
+          <t>-10,63; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 10,76</t>
+          <t>-7,2; 11,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,09; 739,72</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 13,29</t>
+          <t>-3,32; 12,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 11,62</t>
+          <t>-7,64; 10,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 16,16</t>
+          <t>-4,42; 14,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 8,19</t>
+          <t>-4,55; 6,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,28; —</t>
+          <t>-87,63; 1061,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,05; 711,98</t>
+          <t>-70,4; 695,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-31,29; -4,3</t>
+          <t>-30,63; -3,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 2,85</t>
+          <t>-17,11; 2,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 0,0</t>
+          <t>-16,54; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 17,28</t>
+          <t>1,77; 15,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 10,68</t>
+          <t>-13,37; 10,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-21,87; 4,1</t>
+          <t>-22,61; 3,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 12,24</t>
+          <t>-4,01; 11,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 3,87</t>
+          <t>-14,72; 3,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 345,62</t>
+          <t>-100,0; 356,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 134,61</t>
+          <t>-100,0; 97,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,32 +1260,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 3,83</t>
+          <t>-9,48; 3,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 8,78</t>
+          <t>-4,43; 8,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 12,21</t>
+          <t>1,98; 11,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 7,93</t>
+          <t>-4,07; 7,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-89,24; 148,36</t>
+          <t>-86,27; 117,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 1128,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-61,67; 323,97</t>
+          <t>-56,62; 306,64</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 2,48</t>
+          <t>-9,52; 3,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 6,52</t>
+          <t>-4,2; 7,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 7,51</t>
+          <t>-2,24; 7,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,97</t>
+          <t>-2,0; 5,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-83,62; 63,43</t>
+          <t>-79,84; 101,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,98; 311,25</t>
+          <t>-66,74; 395,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-75,59; 920,58</t>
+          <t>-70,15; 862,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 1,87</t>
+          <t>-4,14; 1,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 3,84</t>
+          <t>-2,24; 3,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 4,03</t>
+          <t>-1,13; 3,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,14</t>
+          <t>-0,88; 3,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-47,95; 32,59</t>
+          <t>-47,21; 37,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 83,87</t>
+          <t>-32,55; 80,41</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 159,24</t>
+          <t>-23,29; 138,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 191,18</t>
+          <t>-25,33; 155,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C04-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 25,33</t>
+          <t>-8,05; 22,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,3; 9,63</t>
+          <t>-19,24; 9,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 13,85</t>
+          <t>-12,22; 12,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 21,72</t>
+          <t>-5,34; 21,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-99,4; 158,48</t>
+          <t>-93,68; 241,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 4,63</t>
+          <t>-10,03; 3,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 11,73</t>
+          <t>-1,0; 11,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 0,66</t>
+          <t>-13,77; 0,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 6,64</t>
+          <t>-2,78; 6,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-87,4; 203,26</t>
+          <t>-88,65; 118,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,2; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 74,51</t>
+          <t>-100,0; 79,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 17,94</t>
+          <t>0,43; 19,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,54</t>
+          <t>0,05; 19,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 0,0</t>
+          <t>-10,74; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 11,84</t>
+          <t>-6,52; 11,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-89,09; 739,72</t>
+          <t>-77,56; 631,42</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 12,63</t>
+          <t>-3,44; 12,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 10,7</t>
+          <t>-8,68; 10,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 14,54</t>
+          <t>-3,86; 14,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 6,77</t>
+          <t>-4,92; 6,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-79,24; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-87,63; 1061,64</t>
+          <t>-80,96; 790,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-70,4; 695,26</t>
+          <t>-63,63; 738,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-30,63; -3,25</t>
+          <t>-30,94; -3,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 2,95</t>
+          <t>-16,42; 2,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 0,0</t>
+          <t>-18,68; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 15,89</t>
+          <t>1,77; 15,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 10,79</t>
+          <t>-11,89; 9,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,61; 3,65</t>
+          <t>-20,39; 4,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 11,63</t>
+          <t>-4,04; 11,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 3,71</t>
+          <t>-14,36; 4,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 356,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 97,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1260,32 +1260,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 3,34</t>
+          <t>-9,22; 3,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 8,25</t>
+          <t>-4,37; 8,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 11,98</t>
+          <t>2,13; 12,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 7,64</t>
+          <t>-3,83; 8,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-86,27; 117,43</t>
+          <t>-87,3; 139,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1128,91</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-56,62; 306,64</t>
+          <t>-51,17; 323,81</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 3,65</t>
+          <t>-10,21; 3,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 7,02</t>
+          <t>-4,49; 6,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 7,25</t>
+          <t>-2,12; 7,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 5,91</t>
+          <t>-2,02; 5,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-79,84; 101,68</t>
+          <t>-77,91; 97,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,74; 395,24</t>
+          <t>-68,22; 369,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-70,15; 862,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 1,77</t>
+          <t>-4,3; 1,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,57</t>
+          <t>-2,29; 3,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,84</t>
+          <t>-0,99; 4,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,88</t>
+          <t>-0,87; 3,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-47,21; 37,09</t>
+          <t>-49,46; 38,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-32,55; 80,41</t>
+          <t>-31,09; 93,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 138,22</t>
+          <t>-20,74; 158,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 155,73</t>
+          <t>-23,85; 168,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C04-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,95</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 22,58</t>
+          <t>-8,16; 22,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,24; 9,95</t>
+          <t>-19,04; 10,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 12,21</t>
+          <t>-11,23; 11,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 21,14</t>
+          <t>-8,14; 10,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-93,68; 241,82</t>
+          <t>-100,0; 181,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>2,11</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>130,86%</t>
+          <t>150,19%</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 3,26</t>
+          <t>-8,97; 3,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 11,34</t>
+          <t>-0,96; 11,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 0,93</t>
+          <t>-12,72; 0,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 6,67</t>
+          <t>-2,46; 6,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,65; 118,18</t>
+          <t>-87,11; 122,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-71,64; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 79,42</t>
+          <t>-100,0; 168,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 19,65</t>
+          <t>0,11; 19,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 19,53</t>
+          <t>-0,95; 16,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 0,0</t>
+          <t>-10,45; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 11,7</t>
+          <t>-8,15; 10,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-77,56; 631,42</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>-2,23%</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 12,63</t>
+          <t>-3,52; 13,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 10,7</t>
+          <t>-7,44; 11,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 14,38</t>
+          <t>-4,45; 16,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 6,83</t>
+          <t>-6,86; 4,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-79,24; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-80,96; 790,45</t>
+          <t>-78,28; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,63; 738,36</t>
+          <t>-59,05; 711,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,18</t>
+          <t>6,23</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-30,94; -3,26</t>
+          <t>-31,29; -4,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 2,92</t>
+          <t>-16,67; 2,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 0,0</t>
+          <t>-18,02; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 15,93</t>
+          <t>1,86; 17,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,9</t>
+          <t>-3,19</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-58,61%</t>
+          <t>-55,89%</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 9,5</t>
+          <t>-13,47; 10,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 4,06</t>
+          <t>-21,87; 4,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 11,75</t>
+          <t>-4,49; 12,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 4,36</t>
+          <t>-12,99; 3,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 345,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 134,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>1,34</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -1260,27 +1260,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 3,94</t>
+          <t>-9,73; 3,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 8,5</t>
+          <t>-4,29; 8,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 12,3</t>
+          <t>2,2; 12,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 8,2</t>
+          <t>-5,01; 8,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-87,3; 139,32</t>
+          <t>-89,24; 148,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-51,17; 323,81</t>
+          <t>-64,27; 352,06</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>102,13%</t>
+          <t>142,65%</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 3,37</t>
+          <t>-10,12; 2,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 6,87</t>
+          <t>-4,66; 6,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 7,48</t>
+          <t>-2,27; 7,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 5,23</t>
+          <t>-1,55; 5,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-77,91; 97,38</t>
+          <t>-83,62; 63,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,22; 369,26</t>
+          <t>-68,98; 311,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-75,59; 920,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,9</t>
+          <t>-4,16; 1,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 3,86</t>
+          <t>-2,37; 3,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 4,07</t>
+          <t>-1,23; 4,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 3,76</t>
+          <t>-0,81; 3,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-49,46; 38,85</t>
+          <t>-47,95; 32,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-31,09; 93,91</t>
+          <t>-33,33; 83,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-20,74; 158,49</t>
+          <t>-25,25; 159,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-23,85; 168,21</t>
+          <t>-21,22; 171,28</t>
         </is>
       </c>
     </row>
